--- a/new-info1/web.xlsx
+++ b/new-info1/web.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="13440" windowHeight="5730"/>
+    <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet5" sheetId="10" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="17">
   <si>
     <t>domain</t>
   </si>
@@ -40,10 +40,34 @@
     <t>color2</t>
   </si>
   <si>
-    <t>read.windrise.cloud</t>
-  </si>
-  <si>
-    <t>#f0cfe3</t>
+    <t>nainsook.fun</t>
+  </si>
+  <si>
+    <t>#bd9683</t>
+  </si>
+  <si>
+    <t>quittor.fun</t>
+  </si>
+  <si>
+    <t>#bdeae5</t>
+  </si>
+  <si>
+    <t>keelhaul.fun</t>
+  </si>
+  <si>
+    <t>#36B06F</t>
+  </si>
+  <si>
+    <t>nacreous.site</t>
+  </si>
+  <si>
+    <t>#ff9988</t>
+  </si>
+  <si>
+    <t>oloroso.site</t>
+  </si>
+  <si>
+    <t>#30abc5</t>
   </si>
   <si>
     <t>invicts.site</t>
@@ -68,7 +92,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="25">
+  <fonts count="23">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -92,24 +116,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="10"/>
-      <color rgb="FF2972F4"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="10"/>
-      <color rgb="FF175CEB"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -259,7 +267,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="36">
+  <fills count="40">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -280,7 +288,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF0CFE3"/>
+        <fgColor rgb="FFBD9683"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBDEAE5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF36B06F"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF9988"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF30ABC5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -471,27 +503,12 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="9">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -610,137 +627,137 @@
     <xf numFmtId="42" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="10" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="11" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="11" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="12" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -751,19 +768,25 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1176,34 +1199,51 @@
       <c r="C2" s="6"/>
     </row>
     <row r="3" spans="1:5">
-      <c r="A3" s="7"/>
-      <c r="B3" s="8"/>
+      <c r="A3" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>6</v>
+      </c>
       <c r="E3" s="6"/>
     </row>
     <row r="4" spans="1:5">
-      <c r="A4" s="6"/>
-      <c r="B4" s="6"/>
+      <c r="A4" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4" s="8" t="s">
+        <v>8</v>
+      </c>
       <c r="D4" s="6"/>
       <c r="E4" s="6"/>
     </row>
     <row r="5" spans="1:5">
-      <c r="A5" s="6"/>
-      <c r="B5" s="6"/>
+      <c r="A5" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" s="9" t="s">
+        <v>10</v>
+      </c>
       <c r="D5" s="6"/>
       <c r="E5" s="6"/>
     </row>
     <row r="6" spans="1:5">
-      <c r="A6" s="6"/>
-      <c r="B6" s="6"/>
+      <c r="A6" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6" s="10" t="s">
+        <v>12</v>
+      </c>
       <c r="D6" s="6"/>
       <c r="E6" s="6"/>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="A4" r:id="rId1"/>
-    <hyperlink ref="A5" r:id="rId2"/>
-    <hyperlink ref="A6" r:id="rId3"/>
-    <hyperlink ref="A2" r:id="rId4" display="read.windrise.cloud" tooltip="http://windrise.cloud"/>
+    <hyperlink ref="A2" r:id="rId1" display="nainsook.fun"/>
+    <hyperlink ref="A3" r:id="rId2" display="quittor.fun"/>
+    <hyperlink ref="A4" r:id="rId3" display="keelhaul.fun"/>
+    <hyperlink ref="A5" r:id="rId4" display="nacreous.site"/>
+    <hyperlink ref="A6" r:id="rId5" display="oloroso.site"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
@@ -1229,18 +1269,18 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="1" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>6</v>
+        <v>14</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="1" t="s">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
     </row>
   </sheetData>

--- a/new-info1/web.xlsx
+++ b/new-info1/web.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="13">
   <si>
     <t>domain</t>
   </si>
@@ -40,34 +40,22 @@
     <t>color2</t>
   </si>
   <si>
-    <t>nainsook.fun</t>
+    <t>read.defeasance.site</t>
   </si>
   <si>
-    <t>#bd9683</t>
+    <t>#92cff4</t>
   </si>
   <si>
-    <t>quittor.fun</t>
+    <t>sec.defeasance.site</t>
   </si>
   <si>
-    <t>#bdeae5</t>
+    <t>#ba7ac7</t>
   </si>
   <si>
-    <t>keelhaul.fun</t>
+    <t>necrosia.cloud</t>
   </si>
   <si>
-    <t>#36B06F</t>
-  </si>
-  <si>
-    <t>nacreous.site</t>
-  </si>
-  <si>
-    <t>#ff9988</t>
-  </si>
-  <si>
-    <t>oloroso.site</t>
-  </si>
-  <si>
-    <t>#30abc5</t>
+    <t>green</t>
   </si>
   <si>
     <t>invicts.site</t>
@@ -288,13 +276,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFBD9683"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBDEAE5"/>
+        <fgColor rgb="FF92CFF4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBA7AC7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -757,7 +745,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -768,16 +756,19 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1175,7 +1166,7 @@
   <dimension ref="A1:E6"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="5" outlineLevelCol="4"/>
   <cols>
-    <col min="1" max="1" width="20" customWidth="1"/>
+    <col min="1" max="1" width="28.5" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -1196,55 +1187,39 @@
       <c r="B2" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="6"/>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="7" t="s">
+      <c r="B3" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="E3" s="6"/>
+      <c r="E3" s="7"/>
     </row>
     <row r="4" spans="1:5">
-      <c r="A4" s="4" t="s">
+      <c r="A4" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="8" t="s">
+      <c r="B4" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="D4" s="6"/>
-      <c r="E4" s="6"/>
+      <c r="D4" s="7"/>
+      <c r="E4" s="7"/>
     </row>
     <row r="5" spans="1:5">
-      <c r="A5" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="B5" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="D5" s="6"/>
-      <c r="E5" s="6"/>
+      <c r="A5" s="1"/>
+      <c r="B5" s="10"/>
+      <c r="D5" s="7"/>
+      <c r="E5" s="7"/>
     </row>
     <row r="6" spans="1:5">
-      <c r="A6" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B6" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="D6" s="6"/>
-      <c r="E6" s="6"/>
+      <c r="A6" s="1"/>
+      <c r="B6" s="11"/>
+      <c r="D6" s="7"/>
+      <c r="E6" s="7"/>
     </row>
   </sheetData>
-  <hyperlinks>
-    <hyperlink ref="A2" r:id="rId1" display="nainsook.fun"/>
-    <hyperlink ref="A3" r:id="rId2" display="quittor.fun"/>
-    <hyperlink ref="A4" r:id="rId3" display="keelhaul.fun"/>
-    <hyperlink ref="A5" r:id="rId4" display="nacreous.site"/>
-    <hyperlink ref="A6" r:id="rId5" display="oloroso.site"/>
-  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
@@ -1269,18 +1244,18 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="1" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>
